--- a/batchtest/Results/AnhDThe187386/TC1/GradeDetail.xlsx
+++ b/batchtest/Results/AnhDThe187386/TC1/GradeDetail.xlsx
@@ -71,6 +71,18 @@
     <x:t>ActualExcerpt</x:t>
   </x:si>
   <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>StartClient</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StartServer</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve"> S001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Console</x:t>
   </x:si>
   <x:si>
@@ -129,9 +141,6 @@
   </x:si>
   <x:si>
     <x:t>NetworkResult</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>TCP</x:t>
@@ -536,11 +545,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:Q1"/>
+  <x:dimension ref="A1:Q4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="2" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.853482" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.282054" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
@@ -607,6 +616,39 @@
       </x:c>
       <x:c r="Q1" s="1" t="s">
         <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:17">
+      <x:c r="A2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:17">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:17">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -651,7 +693,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
         <x:v>1</x:v>
@@ -702,7 +744,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -747,7 +789,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
         <x:v>1</x:v>
@@ -798,7 +840,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -859,55 +901,55 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="Q1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="R1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:18">
@@ -915,55 +957,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -971,55 +1013,55 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
